--- a/istakip.xlsx
+++ b/istakip.xlsx
@@ -4033,7 +4033,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L95" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
     </row>
     <row r="96">
@@ -4071,7 +4071,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L96" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
     </row>
     <row r="97">
@@ -4192,7 +4192,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L99" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -4230,7 +4230,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L100" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M100" t="str" xml:space="preserve">
         <v xml:space="preserve">15.10.2025 Projesine başlanılacak(Ormancı kontrolünde)_x000d__x000d__x000d_
@@ -4320,7 +4320,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L102" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M102" t="str" xml:space="preserve">
         <v xml:space="preserve">01.11.2025 firmaya teslim edilecek_x000d__x000d_
@@ -4412,7 +4412,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L104" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
     </row>
     <row r="105">
@@ -4450,7 +4450,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L105" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M105" t="str">
         <v>[x] 21.10.2025 komisyon yapılacak(İsmail Pehlivan)</v>
@@ -4491,7 +4491,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L106" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M106" t="str" xml:space="preserve">
         <v xml:space="preserve">03.11.2025 firmaya teslim edilecek_x000d__x000d_
@@ -4542,7 +4542,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L107" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M107" t="str" xml:space="preserve">
         <v xml:space="preserve">16.10.2025 firmaya teslim edilecek_x000d__x000d__x000d_
@@ -4668,7 +4668,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L110" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M110" t="str" xml:space="preserve">
         <v xml:space="preserve">16.10.2025 Taşçılı tutanak Kadastro Üyesine teslim edilecek._x000d__x000d__x000d_
@@ -4716,7 +4716,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L111" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M111" t="str" xml:space="preserve">
         <v xml:space="preserve">24.10.2025 firmaya teslim edilecek_x000d__x000d_
@@ -4767,7 +4767,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L112" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M112" t="str">
         <v>[x] 20.10.2025 askıya çıkacak</v>
@@ -4854,7 +4854,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L114" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M114" t="str" xml:space="preserve">
         <v xml:space="preserve">14.11.2025 firmaya teslim edilecek_x000d__x000d_
@@ -4902,7 +4902,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L115" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M115" t="str" xml:space="preserve">
         <v xml:space="preserve">Kıymetlendirmede eksiklikler var firma tamamlayacak bu hafta(20.10.2025)_x000d__x000d_
@@ -5001,7 +5001,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L117" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M117" t="str" xml:space="preserve">
         <v xml:space="preserve">01.11.2025 firmaya teslim edilecek_x000d__x000d__x000d_
@@ -5052,7 +5052,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L118" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M118" t="str" xml:space="preserve">
         <v xml:space="preserve">01.11.2025 firmaya teslim edilecek_x000d__x000d_
@@ -5195,7 +5195,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L121" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M121" t="str" xml:space="preserve">
         <v xml:space="preserve">17.10.2025 firmaya teslim edilecek_x000d__x000d__x000d_
@@ -5244,7 +5244,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L122" t="str">
-        <v>DEVİR YAPILDI</v>
+        <v>TESCİLİ BİTTİ</v>
       </c>
       <c r="M122" t="str" xml:space="preserve">
         <v xml:space="preserve">17.10.2025 Tutanaklara başlanılacak_x000d__x000d__x000d_

--- a/istakip.xlsx
+++ b/istakip.xlsx
@@ -5106,7 +5106,7 @@
         <v>2025-05-23</v>
       </c>
       <c r="L119" t="str">
-        <v>KESİN ASKIDA</v>
+        <v>KESİN ASKIDAN İNDİ. BEKLEMEDE</v>
       </c>
       <c r="M119" t="str" xml:space="preserve">
         <v xml:space="preserve">15.12.2025 Değerlendirme devam ediyor_x000d__x000d__x000d_

--- a/istakip.xlsx
+++ b/istakip.xlsx
@@ -7462,7 +7462,7 @@
         <v/>
       </c>
       <c r="L180" t="str">
-        <v>VERİLER ELEKTRONİK ORTAMDA HAZIRLANDI.</v>
+        <v>DEĞERLENDİRMEDE</v>
       </c>
     </row>
     <row r="181">
@@ -7771,7 +7771,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>HAYIR</v>
+        <v>EVET</v>
       </c>
       <c r="B189" t="str">
         <v>Mut</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HAYIR</v>
+        <v>EVET</v>
       </c>
       <c r="B190" t="str">
         <v>Mut</v>
@@ -7880,7 +7880,7 @@
         <v/>
       </c>
       <c r="L191" t="str">
-        <v>ASKI İLANINA HAZIRLANIYOR</v>
+        <v>KESİN ASKIDA</v>
       </c>
     </row>
     <row r="192">
@@ -8236,7 +8236,7 @@
     </row>
     <row r="201" xml:space="preserve">
       <c r="A201" t="str">
-        <v>HAYIR</v>
+        <v>EVET</v>
       </c>
       <c r="B201" t="str">
         <v>Gülnar</v>

--- a/istakip.xlsx
+++ b/istakip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3E1D98-DC04-4109-9260-20F8870CBB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26E44FD-C8C2-4E44-90B9-AF59C1D48926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="859">
   <si>
     <t>Tamamlandı</t>
   </si>
@@ -3115,12 +3115,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M208"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="93.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>115</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>13</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>13</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>13</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>13</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>13</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>13</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>13</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>115</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>115</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>115</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>115</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>115</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>115</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>115</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>115</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>115</v>
       </c>
@@ -7307,7 +7307,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>115</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>115</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>115</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>115</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>115</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>13</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>13</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>13</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>13</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>13</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>13</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>13</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>13</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>13</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>13</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>13</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>13</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>13</v>
       </c>
@@ -9955,8 +9955,11 @@
       <c r="G178" s="1">
         <v>3331</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I178" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>13</v>
       </c>
@@ -9994,7 +9997,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -10035,7 +10038,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>13</v>
       </c>
@@ -10073,7 +10076,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -10111,7 +10114,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>13</v>
       </c>
@@ -10149,7 +10152,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>13</v>
       </c>
@@ -10187,7 +10190,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>13</v>
       </c>
@@ -10225,7 +10228,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -10263,7 +10266,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -10301,7 +10304,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>115</v>
       </c>
@@ -10339,7 +10342,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>13</v>
       </c>
@@ -10377,7 +10380,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>115</v>
       </c>
@@ -10415,7 +10418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>115</v>
       </c>
@@ -10453,7 +10456,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -10491,7 +10494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -10529,7 +10532,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>115</v>
       </c>
@@ -10567,7 +10570,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -10608,7 +10611,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -10646,7 +10649,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -10684,7 +10687,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -10722,7 +10725,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -10760,7 +10763,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -10801,7 +10804,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -10842,7 +10845,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>115</v>
       </c>
@@ -10883,7 +10886,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -10921,7 +10924,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -10962,7 +10965,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -11003,7 +11006,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -11041,7 +11044,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -11079,7 +11082,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -11128,9 +11131,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11177,7 +11180,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>212</v>
       </c>
@@ -11224,7 +11227,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>212</v>
       </c>
@@ -11271,7 +11274,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>212</v>
       </c>
@@ -11318,7 +11321,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>239</v>
       </c>
@@ -11365,7 +11368,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>239</v>
       </c>
@@ -11412,7 +11415,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>239</v>
       </c>
@@ -11459,7 +11462,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -11506,7 +11509,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -11553,7 +11556,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>239</v>
       </c>
@@ -11600,7 +11603,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>239</v>
       </c>
@@ -11647,7 +11650,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -11694,7 +11697,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>193</v>
       </c>
@@ -11741,7 +11744,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>193</v>
       </c>
@@ -11788,7 +11791,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>193</v>
       </c>
@@ -11835,7 +11838,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>193</v>
       </c>
@@ -11882,7 +11885,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -11929,7 +11932,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -11976,7 +11979,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -12023,7 +12026,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>193</v>
       </c>
@@ -12070,7 +12073,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>193</v>
       </c>
@@ -12117,7 +12120,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>193</v>
       </c>
@@ -12164,7 +12167,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>221</v>
       </c>
@@ -12211,7 +12214,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>239</v>
       </c>
@@ -12258,7 +12261,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>239</v>
       </c>
@@ -12305,7 +12308,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>239</v>
       </c>
@@ -12352,7 +12355,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>239</v>
       </c>
@@ -12399,7 +12402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>239</v>
       </c>
@@ -12446,7 +12449,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>252</v>
       </c>
@@ -12493,7 +12496,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -12540,7 +12543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -12587,7 +12590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -12634,7 +12637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -12681,7 +12684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -12728,7 +12731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -12775,7 +12778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -12822,7 +12825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -12869,7 +12872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -12963,7 +12966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -13010,7 +13013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -13057,7 +13060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -13104,7 +13107,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -13151,7 +13154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -13198,7 +13201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -13245,7 +13248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -13292,7 +13295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -13339,7 +13342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -13386,7 +13389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -13433,7 +13436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -13480,7 +13483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -13527,7 +13530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -13574,7 +13577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -13621,7 +13624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>32</v>
       </c>
@@ -13668,7 +13671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -13715,7 +13718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>32</v>
       </c>
@@ -13762,7 +13765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -13809,7 +13812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -13856,7 +13859,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -13903,7 +13906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -13950,7 +13953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -13997,7 +14000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -14044,7 +14047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -14091,7 +14094,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -14138,7 +14141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>101</v>
       </c>
@@ -14185,7 +14188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -14232,7 +14235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -14279,7 +14282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>48</v>
       </c>
@@ -14326,7 +14329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>48</v>
       </c>
@@ -14373,7 +14376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -14420,7 +14423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -14467,7 +14470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -14514,7 +14517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -14561,7 +14564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -14608,7 +14611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -14655,7 +14658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>48</v>
       </c>
@@ -14702,7 +14705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>48</v>
       </c>
@@ -14749,7 +14752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>48</v>
       </c>
@@ -14796,7 +14799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -14843,7 +14846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>48</v>
       </c>
@@ -14890,7 +14893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>48</v>
       </c>
@@ -14937,7 +14940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>48</v>
       </c>
@@ -14984,7 +14987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>48</v>
       </c>
@@ -15042,9 +15045,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>734</v>
       </c>
@@ -15052,7 +15055,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>736</v>
       </c>
@@ -15060,7 +15063,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>738</v>
       </c>
@@ -15068,7 +15071,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>739</v>
       </c>
@@ -15076,7 +15079,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>741</v>
       </c>
@@ -15084,7 +15087,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>742</v>
       </c>
@@ -15092,7 +15095,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>743</v>
       </c>
@@ -15100,7 +15103,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>744</v>
       </c>
@@ -15108,7 +15111,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>745</v>
       </c>
@@ -15116,7 +15119,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>746</v>
       </c>
@@ -15124,7 +15127,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>747</v>
       </c>
@@ -15132,7 +15135,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>748</v>
       </c>
@@ -15140,7 +15143,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>749</v>
       </c>
@@ -15148,7 +15151,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>750</v>
       </c>
@@ -15156,7 +15159,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>751</v>
       </c>
@@ -15164,7 +15167,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>752</v>
       </c>
@@ -15172,7 +15175,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>753</v>
       </c>
@@ -15180,7 +15183,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>754</v>
       </c>
@@ -15188,7 +15191,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>756</v>
       </c>
@@ -15196,7 +15199,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>757</v>
       </c>
@@ -15204,7 +15207,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>758</v>
       </c>
@@ -15212,7 +15215,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>759</v>
       </c>
@@ -15220,7 +15223,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>760</v>
       </c>
@@ -15228,7 +15231,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>762</v>
       </c>
@@ -15236,7 +15239,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>763</v>
       </c>
@@ -15244,7 +15247,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>764</v>
       </c>
@@ -15252,7 +15255,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>765</v>
       </c>
@@ -15260,7 +15263,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>767</v>
       </c>
@@ -15268,7 +15271,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>768</v>
       </c>
@@ -15276,7 +15279,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>769</v>
       </c>
@@ -15284,7 +15287,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>770</v>
       </c>
@@ -15292,7 +15295,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>771</v>
       </c>
@@ -15300,7 +15303,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>772</v>
       </c>
@@ -15308,7 +15311,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>773</v>
       </c>
@@ -15316,7 +15319,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>774</v>
       </c>
@@ -15324,7 +15327,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>776</v>
       </c>
@@ -15332,7 +15335,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>777</v>
       </c>
@@ -15340,7 +15343,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>778</v>
       </c>
@@ -15348,7 +15351,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>779</v>
       </c>
@@ -15356,7 +15359,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>780</v>
       </c>
@@ -15364,7 +15367,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>781</v>
       </c>
@@ -15372,7 +15375,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>782</v>
       </c>
@@ -15380,7 +15383,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>783</v>
       </c>
@@ -15388,7 +15391,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>784</v>
       </c>
@@ -15396,7 +15399,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>785</v>
       </c>
@@ -15404,7 +15407,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>786</v>
       </c>
@@ -15412,7 +15415,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>787</v>
       </c>
@@ -15420,7 +15423,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>788</v>
       </c>
@@ -15428,7 +15431,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>789</v>
       </c>
@@ -15436,7 +15439,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>790</v>
       </c>
@@ -15444,7 +15447,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>791</v>
       </c>
@@ -15452,7 +15455,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>792</v>
       </c>
@@ -15460,7 +15463,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>794</v>
       </c>
@@ -15468,7 +15471,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>795</v>
       </c>
@@ -15476,7 +15479,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>796</v>
       </c>
@@ -15484,7 +15487,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>797</v>
       </c>
@@ -15492,7 +15495,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>798</v>
       </c>
@@ -15500,7 +15503,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>799</v>
       </c>
@@ -15508,7 +15511,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>800</v>
       </c>
@@ -15516,7 +15519,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>801</v>
       </c>
@@ -15524,7 +15527,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>802</v>
       </c>
@@ -15532,7 +15535,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>803</v>
       </c>
@@ -15540,7 +15543,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>804</v>
       </c>
@@ -15548,7 +15551,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>805</v>
       </c>
@@ -15556,7 +15559,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>806</v>
       </c>
@@ -15564,7 +15567,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>807</v>
       </c>
@@ -15572,7 +15575,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>808</v>
       </c>
@@ -15580,7 +15583,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>809</v>
       </c>
@@ -15588,7 +15591,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>810</v>
       </c>
@@ -15596,7 +15599,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>811</v>
       </c>
@@ -15604,7 +15607,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>812</v>
       </c>
@@ -15612,7 +15615,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>813</v>
       </c>
@@ -15620,7 +15623,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>814</v>
       </c>
@@ -15628,7 +15631,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>815</v>
       </c>
@@ -15636,7 +15639,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>816</v>
       </c>
@@ -15644,7 +15647,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>817</v>
       </c>
@@ -15652,7 +15655,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>818</v>
       </c>
@@ -15660,7 +15663,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>819</v>
       </c>
@@ -15679,74 +15682,74 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>252</v>
       </c>
@@ -15762,34 +15765,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7139</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>522</v>
       </c>
@@ -15805,9 +15808,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>594</v>
       </c>
@@ -15821,7 +15824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>603</v>
       </c>
@@ -15835,7 +15838,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>823</v>
       </c>
@@ -15849,7 +15852,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -15863,7 +15866,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -15877,7 +15880,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -15891,7 +15894,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -15905,7 +15908,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -15919,7 +15922,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -15933,7 +15936,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -15947,7 +15950,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -15961,7 +15964,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -15975,7 +15978,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -15989,7 +15992,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -16003,7 +16006,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -16017,7 +16020,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -16031,7 +16034,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -16045,7 +16048,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -16059,7 +16062,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -16073,7 +16076,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -16087,7 +16090,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -16101,7 +16104,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -16115,7 +16118,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -16129,7 +16132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -16143,7 +16146,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -16157,7 +16160,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -16182,9 +16185,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C92"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16195,7 +16198,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>212</v>
       </c>
@@ -16206,7 +16209,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>212</v>
       </c>
@@ -16217,7 +16220,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>212</v>
       </c>
@@ -16228,7 +16231,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>239</v>
       </c>
@@ -16239,7 +16242,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>239</v>
       </c>
@@ -16250,7 +16253,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>239</v>
       </c>
@@ -16261,7 +16264,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -16272,7 +16275,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -16283,7 +16286,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>239</v>
       </c>
@@ -16294,7 +16297,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>239</v>
       </c>
@@ -16305,7 +16308,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -16316,7 +16319,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>193</v>
       </c>
@@ -16327,7 +16330,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>193</v>
       </c>
@@ -16338,7 +16341,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>193</v>
       </c>
@@ -16349,7 +16352,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>193</v>
       </c>
@@ -16360,7 +16363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -16371,7 +16374,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -16382,7 +16385,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -16393,7 +16396,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>193</v>
       </c>
@@ -16404,7 +16407,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>193</v>
       </c>
@@ -16415,7 +16418,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>193</v>
       </c>
@@ -16426,7 +16429,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>221</v>
       </c>
@@ -16437,7 +16440,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>239</v>
       </c>
@@ -16448,7 +16451,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>239</v>
       </c>
@@ -16459,7 +16462,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>239</v>
       </c>
@@ -16470,7 +16473,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>239</v>
       </c>
@@ -16481,7 +16484,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>239</v>
       </c>
@@ -16492,7 +16495,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>252</v>
       </c>
@@ -16503,7 +16506,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -16514,7 +16517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -16525,7 +16528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -16536,7 +16539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -16547,7 +16550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -16558,7 +16561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -16569,7 +16572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -16580,7 +16583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -16591,7 +16594,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -16602,7 +16605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -16613,7 +16616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -16624,7 +16627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -16635,7 +16638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -16646,7 +16649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -16657,7 +16660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -16668,7 +16671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -16679,7 +16682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -16690,7 +16693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -16701,7 +16704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -16712,7 +16715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -16723,7 +16726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -16734,7 +16737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -16745,7 +16748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -16756,7 +16759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -16767,7 +16770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>32</v>
       </c>
@@ -16778,7 +16781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -16789,7 +16792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>32</v>
       </c>
@@ -16800,7 +16803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -16811,7 +16814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -16822,7 +16825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -16833,7 +16836,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -16844,7 +16847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -16855,7 +16858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -16866,7 +16869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -16877,7 +16880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -16888,7 +16891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>101</v>
       </c>
@@ -16899,7 +16902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -16910,7 +16913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>48</v>
       </c>
@@ -16921,7 +16924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>48</v>
       </c>
@@ -16932,7 +16935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>48</v>
       </c>
@@ -16943,7 +16946,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -16954,7 +16957,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -16965,7 +16968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -16976,7 +16979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -16987,7 +16990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -16998,7 +17001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -17009,7 +17012,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>48</v>
       </c>
@@ -17020,7 +17023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>48</v>
       </c>
@@ -17031,7 +17034,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>48</v>
       </c>
@@ -17042,7 +17045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -17053,7 +17056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>48</v>
       </c>
@@ -17064,7 +17067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>48</v>
       </c>
@@ -17075,7 +17078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>48</v>
       </c>
@@ -17086,7 +17089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>48</v>
       </c>
@@ -17097,7 +17100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>252</v>
       </c>
@@ -17108,7 +17111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>182</v>
       </c>
@@ -17119,7 +17122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>239</v>
       </c>
@@ -17130,7 +17133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>239</v>
       </c>
@@ -17141,7 +17144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>239</v>
       </c>
@@ -17152,7 +17155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>123</v>
       </c>
@@ -17163,7 +17166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -17174,7 +17177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -17185,7 +17188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>32</v>
       </c>
